--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/67.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/67.xlsx
@@ -426,13 +426,13 @@
         <v>-3.396357643436828</v>
       </c>
       <c r="E2">
-        <v>-18.50538468535213</v>
+        <v>-28.74456329597932</v>
       </c>
       <c r="F2">
-        <v>-6.101645782621476</v>
+        <v>-5.823869308024102</v>
       </c>
       <c r="G2">
-        <v>-7.359261120829701</v>
+        <v>-16.3874035133386</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.046344255705005</v>
       </c>
       <c r="E3">
-        <v>-19.69514613291336</v>
+        <v>-28.70686827833947</v>
       </c>
       <c r="F3">
-        <v>-6.070799150653505</v>
+        <v>-6.458193809820416</v>
       </c>
       <c r="G3">
-        <v>-8.279953630210871</v>
+        <v>-15.10083613204826</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.742941679438852</v>
       </c>
       <c r="E4">
-        <v>-20.62582905402176</v>
+        <v>-28.06867043643849</v>
       </c>
       <c r="F4">
-        <v>-5.893386079182316</v>
+        <v>-6.276526508333878</v>
       </c>
       <c r="G4">
-        <v>-6.936544182011241</v>
+        <v>-16.55935490392112</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.513853635319517</v>
       </c>
       <c r="E5">
-        <v>-20.73675855331365</v>
+        <v>-28.76539880488861</v>
       </c>
       <c r="F5">
-        <v>-5.795622329316323</v>
+        <v>-6.29829217058272</v>
       </c>
       <c r="G5">
-        <v>-7.781647005094233</v>
+        <v>-15.49742293492525</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.338050406567599</v>
       </c>
       <c r="E6">
-        <v>-20.85201727375687</v>
+        <v>-29.99686296958647</v>
       </c>
       <c r="F6">
-        <v>-6.14727116226585</v>
+        <v>-6.691307006117046</v>
       </c>
       <c r="G6">
-        <v>-6.969907859956017</v>
+        <v>-16.14041529756297</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.200592966418745</v>
       </c>
       <c r="E7">
-        <v>-21.80391609559121</v>
+        <v>-29.86983474519731</v>
       </c>
       <c r="F7">
-        <v>-6.128276193516069</v>
+        <v>-6.454780527646165</v>
       </c>
       <c r="G7">
-        <v>-7.056124397435256</v>
+        <v>-15.37022515421538</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.080631257686765</v>
       </c>
       <c r="E8">
-        <v>-21.36487601207356</v>
+        <v>-29.65235704521595</v>
       </c>
       <c r="F8">
-        <v>-6.357466946186635</v>
+        <v>-6.275200154629697</v>
       </c>
       <c r="G8">
-        <v>-7.745012508156658</v>
+        <v>-14.47044701627855</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.955717132049891</v>
       </c>
       <c r="E9">
-        <v>-21.79722753948188</v>
+        <v>-31.1620665026041</v>
       </c>
       <c r="F9">
-        <v>-6.161598949682832</v>
+        <v>-6.422651885739644</v>
       </c>
       <c r="G9">
-        <v>-7.034784620889114</v>
+        <v>-14.75826087964448</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.799944987380954</v>
       </c>
       <c r="E10">
-        <v>-23.24253077529594</v>
+        <v>-31.53085184036675</v>
       </c>
       <c r="F10">
-        <v>-6.261079832687639</v>
+        <v>-6.007585529038739</v>
       </c>
       <c r="G10">
-        <v>-7.05683285418066</v>
+        <v>-15.16807000140532</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.599165495588812</v>
       </c>
       <c r="E11">
-        <v>-23.83742734873558</v>
+        <v>-32.19213584275884</v>
       </c>
       <c r="F11">
-        <v>-5.802488486312711</v>
+        <v>-5.982414107218744</v>
       </c>
       <c r="G11">
-        <v>-6.620800901203252</v>
+        <v>-14.89904348397476</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.339899882038983</v>
       </c>
       <c r="E12">
-        <v>-24.06514619268529</v>
+        <v>-30.74412457948819</v>
       </c>
       <c r="F12">
-        <v>-6.077864854595238</v>
+        <v>-5.763252964110657</v>
       </c>
       <c r="G12">
-        <v>-6.327579261698925</v>
+        <v>-13.82818131838671</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.014467241351189</v>
       </c>
       <c r="E13">
-        <v>-24.48197863966933</v>
+        <v>-33.73687078235932</v>
       </c>
       <c r="F13">
-        <v>-6.121145161705325</v>
+        <v>-6.032955705951122</v>
       </c>
       <c r="G13">
-        <v>-5.675034319907642</v>
+        <v>-13.36729544477322</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.6291520285497602</v>
       </c>
       <c r="E14">
-        <v>-25.53227667321633</v>
+        <v>-32.09742960159942</v>
       </c>
       <c r="F14">
-        <v>-5.96172932425719</v>
+        <v>-5.965833498137052</v>
       </c>
       <c r="G14">
-        <v>-4.786080010611464</v>
+        <v>-14.63251642842634</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.1935563164409968</v>
       </c>
       <c r="E15">
-        <v>-26.86778252824042</v>
+        <v>-33.51829039895708</v>
       </c>
       <c r="F15">
-        <v>-5.839041210694011</v>
+        <v>-5.72091021090251</v>
       </c>
       <c r="G15">
-        <v>-5.72768854670975</v>
+        <v>-13.09663848366456</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.2795061132685302</v>
       </c>
       <c r="E16">
-        <v>-26.76290759869678</v>
+        <v>-33.5647049932987</v>
       </c>
       <c r="F16">
-        <v>-5.941125310297322</v>
+        <v>-5.873738623595374</v>
       </c>
       <c r="G16">
-        <v>-5.454227553529332</v>
+        <v>-14.06644790193913</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.7674123963880852</v>
       </c>
       <c r="E17">
-        <v>-27.26539160306189</v>
+        <v>-33.7589969063608</v>
       </c>
       <c r="F17">
-        <v>-5.08993168377904</v>
+        <v>-5.3699221792462</v>
       </c>
       <c r="G17">
-        <v>-4.492500832188895</v>
+        <v>-13.36595136328427</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.248005171209232</v>
       </c>
       <c r="E18">
-        <v>-27.69813257923487</v>
+        <v>-34.75876396269321</v>
       </c>
       <c r="F18">
-        <v>-5.606435988069758</v>
+        <v>-5.502647029048476</v>
       </c>
       <c r="G18">
-        <v>-4.234705340500309</v>
+        <v>-13.87874328040799</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.702218946836501</v>
       </c>
       <c r="E19">
-        <v>-28.77629884182507</v>
+        <v>-35.93488111806932</v>
       </c>
       <c r="F19">
-        <v>-4.788524733217393</v>
+        <v>-5.255524766150347</v>
       </c>
       <c r="G19">
-        <v>-4.072885874540733</v>
+        <v>-13.26895237898363</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.108339824632918</v>
       </c>
       <c r="E20">
-        <v>-30.66015308596396</v>
+        <v>-36.37356798061438</v>
       </c>
       <c r="F20">
-        <v>-5.070110812394359</v>
+        <v>-4.394923134641397</v>
       </c>
       <c r="G20">
-        <v>-4.718753445979305</v>
+        <v>-11.84029307260223</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.449486257284998</v>
       </c>
       <c r="E21">
-        <v>-30.14098165488058</v>
+        <v>-37.07394403487768</v>
       </c>
       <c r="F21">
-        <v>-4.523923899983517</v>
+        <v>-4.405244937945273</v>
       </c>
       <c r="G21">
-        <v>-4.261868366650028</v>
+        <v>-13.01788722637638</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.71563050464258</v>
       </c>
       <c r="E22">
-        <v>-30.48148440822833</v>
+        <v>-37.1131560913101</v>
       </c>
       <c r="F22">
-        <v>-4.683790301764595</v>
+        <v>-4.484550595366819</v>
       </c>
       <c r="G22">
-        <v>-3.832301909110817</v>
+        <v>-12.54815723035473</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.898179737840203</v>
       </c>
       <c r="E23">
-        <v>-31.32084385826104</v>
+        <v>-36.68084079169383</v>
       </c>
       <c r="F23">
-        <v>-4.37834015000083</v>
+        <v>-4.112789885070648</v>
       </c>
       <c r="G23">
-        <v>-3.882175277659937</v>
+        <v>-11.79964950501659</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.99435574003779</v>
       </c>
       <c r="E24">
-        <v>-32.54787011843138</v>
+        <v>-38.1974652288917</v>
       </c>
       <c r="F24">
-        <v>-4.097024092682449</v>
+        <v>-4.698654173633951</v>
       </c>
       <c r="G24">
-        <v>-3.918170839308433</v>
+        <v>-11.67573247493613</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.007505605067216</v>
       </c>
       <c r="E25">
-        <v>-31.76554453428827</v>
+        <v>-38.43625392755317</v>
       </c>
       <c r="F25">
-        <v>-4.110553692318048</v>
+        <v>-5.232594288200699</v>
       </c>
       <c r="G25">
-        <v>-3.288455419555965</v>
+        <v>-12.02566375952818</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.943606429944161</v>
       </c>
       <c r="E26">
-        <v>-31.99382038054093</v>
+        <v>-38.45565843867603</v>
       </c>
       <c r="F26">
-        <v>-4.008182150091084</v>
+        <v>-4.62525415557108</v>
       </c>
       <c r="G26">
-        <v>-4.568361983221294</v>
+        <v>-11.39913639513003</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.812328519720264</v>
       </c>
       <c r="E27">
-        <v>-31.71216061844885</v>
+        <v>-37.69978593544873</v>
       </c>
       <c r="F27">
-        <v>-4.141883354590228</v>
+        <v>-4.55747866906689</v>
       </c>
       <c r="G27">
-        <v>-3.638946186344144</v>
+        <v>-11.22081385965718</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.628118259446614</v>
       </c>
       <c r="E28">
-        <v>-31.04826142231734</v>
+        <v>-38.6340554079712</v>
       </c>
       <c r="F28">
-        <v>-4.327922080329858</v>
+        <v>-4.757347106713095</v>
       </c>
       <c r="G28">
-        <v>-4.842948561885065</v>
+        <v>-11.57172837627439</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.408442444428769</v>
       </c>
       <c r="E29">
-        <v>-33.00151453062377</v>
+        <v>-37.54197540899243</v>
       </c>
       <c r="F29">
-        <v>-4.11093457359071</v>
+        <v>-4.620221930024771</v>
       </c>
       <c r="G29">
-        <v>-3.094417724408201</v>
+        <v>-11.8300734185225</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.171771606916614</v>
       </c>
       <c r="E30">
-        <v>-31.81392901482323</v>
+        <v>-37.80772890613257</v>
       </c>
       <c r="F30">
-        <v>-4.322682389308627</v>
+        <v>-4.649875239585459</v>
       </c>
       <c r="G30">
-        <v>-4.485287153458823</v>
+        <v>-12.6453945739342</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.93862911515045</v>
       </c>
       <c r="E31">
-        <v>-31.92489021343318</v>
+        <v>-38.12805504353913</v>
       </c>
       <c r="F31">
-        <v>-4.005958626985807</v>
+        <v>-4.736496826483377</v>
       </c>
       <c r="G31">
-        <v>-3.81048541400702</v>
+        <v>-12.09407287255168</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.730463889212697</v>
       </c>
       <c r="E32">
-        <v>-31.29100347878749</v>
+        <v>-36.38500464172075</v>
       </c>
       <c r="F32">
-        <v>-3.961653662148431</v>
+        <v>-4.072722917262988</v>
       </c>
       <c r="G32">
-        <v>-5.528632064524452</v>
+        <v>-12.0474570808132</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.564647624660097</v>
       </c>
       <c r="E33">
-        <v>-31.4544270487763</v>
+        <v>-36.88283337480597</v>
       </c>
       <c r="F33">
-        <v>-4.132163359534219</v>
+        <v>-5.208620939905734</v>
       </c>
       <c r="G33">
-        <v>-4.810879307246144</v>
+        <v>-11.91238020171986</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.457642932716085</v>
       </c>
       <c r="E34">
-        <v>-30.39708497391037</v>
+        <v>-35.73407046667319</v>
       </c>
       <c r="F34">
-        <v>-4.189978919536209</v>
+        <v>-4.792463409829091</v>
       </c>
       <c r="G34">
-        <v>-4.531363326274399</v>
+        <v>-12.55747310550224</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.42298587863866</v>
       </c>
       <c r="E35">
-        <v>-29.90959474698466</v>
+        <v>-36.48477598105774</v>
       </c>
       <c r="F35">
-        <v>-4.474822681781233</v>
+        <v>-4.523506593474798</v>
       </c>
       <c r="G35">
-        <v>-5.389612325693837</v>
+        <v>-14.07252606354923</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.465743367403308</v>
       </c>
       <c r="E36">
-        <v>-29.86495305021704</v>
+        <v>-36.55957278624243</v>
       </c>
       <c r="F36">
-        <v>-3.994330266301693</v>
+        <v>-4.688032258059099</v>
       </c>
       <c r="G36">
-        <v>-5.657594366006761</v>
+        <v>-12.11123474062726</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.589269717465293</v>
       </c>
       <c r="E37">
-        <v>-28.52694294906671</v>
+        <v>-36.75095515475459</v>
       </c>
       <c r="F37">
-        <v>-4.380867744641872</v>
+        <v>-4.420343990143073</v>
       </c>
       <c r="G37">
-        <v>-3.836973088866729</v>
+        <v>-12.25582943814601</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.791786650229513</v>
       </c>
       <c r="E38">
-        <v>-28.50863885712771</v>
+        <v>-35.9382887947601</v>
       </c>
       <c r="F38">
-        <v>-4.314678339611995</v>
+        <v>-4.383754048672761</v>
       </c>
       <c r="G38">
-        <v>-3.942099462466286</v>
+        <v>-12.78746332520649</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.062034358798722</v>
       </c>
       <c r="E39">
-        <v>-28.3172338462455</v>
+        <v>-36.09099346677275</v>
       </c>
       <c r="F39">
-        <v>-4.092247635641483</v>
+        <v>-4.366072763979837</v>
       </c>
       <c r="G39">
-        <v>-3.953179858386226</v>
+        <v>-12.97603862021445</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.389952707772376</v>
       </c>
       <c r="E40">
-        <v>-28.2524087408257</v>
+        <v>-35.6727934206384</v>
       </c>
       <c r="F40">
-        <v>-4.31751713246542</v>
+        <v>-4.278428894913502</v>
       </c>
       <c r="G40">
-        <v>-3.747826718585234</v>
+        <v>-12.74169172258052</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.761840095369008</v>
       </c>
       <c r="E41">
-        <v>-27.84854131492563</v>
+        <v>-34.59659930847853</v>
       </c>
       <c r="F41">
-        <v>-4.168245723258633</v>
+        <v>-3.765767453026598</v>
       </c>
       <c r="G41">
-        <v>-4.702197407737411</v>
+        <v>-13.14582325874152</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.156725191121883</v>
       </c>
       <c r="E42">
-        <v>-28.05941876404082</v>
+        <v>-33.33847828153452</v>
       </c>
       <c r="F42">
-        <v>-4.152972463410135</v>
+        <v>-4.038233761689505</v>
       </c>
       <c r="G42">
-        <v>-3.152382066255301</v>
+        <v>-12.39380635513175</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.559035745712237</v>
       </c>
       <c r="E43">
-        <v>-27.34057332853723</v>
+        <v>-35.18963694333802</v>
       </c>
       <c r="F43">
-        <v>-3.803581599169546</v>
+        <v>-3.685229672402841</v>
       </c>
       <c r="G43">
-        <v>-4.328714902178993</v>
+        <v>-12.61418937168103</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.952570899526857</v>
       </c>
       <c r="E44">
-        <v>-25.41199587509859</v>
+        <v>-34.83555329644128</v>
       </c>
       <c r="F44">
-        <v>-3.75411612860671</v>
+        <v>-4.453022178002251</v>
       </c>
       <c r="G44">
-        <v>-4.125646038800098</v>
+        <v>-12.9022300074164</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.317654731241236</v>
       </c>
       <c r="E45">
-        <v>-25.25399288849697</v>
+        <v>-33.57300342191776</v>
       </c>
       <c r="F45">
-        <v>-4.258794900826842</v>
+        <v>-4.073437960483808</v>
       </c>
       <c r="G45">
-        <v>-5.133342995498855</v>
+        <v>-13.69984636528409</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.642670980921732</v>
       </c>
       <c r="E46">
-        <v>-25.53257102402683</v>
+        <v>-33.54346418596572</v>
       </c>
       <c r="F46">
-        <v>-3.835536033425368</v>
+        <v>-4.237669055767837</v>
       </c>
       <c r="G46">
-        <v>-3.914999336681811</v>
+        <v>-12.44877796381135</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.917627804399677</v>
       </c>
       <c r="E47">
-        <v>-23.92695980834123</v>
+        <v>-32.94613582198397</v>
       </c>
       <c r="F47">
-        <v>-4.118507063425384</v>
+        <v>-4.331760191615926</v>
       </c>
       <c r="G47">
-        <v>-5.192840119930636</v>
+        <v>-13.9803290255533</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.132130747265058</v>
       </c>
       <c r="E48">
-        <v>-24.88849975133789</v>
+        <v>-33.11018884985985</v>
       </c>
       <c r="F48">
-        <v>-3.767474688003442</v>
+        <v>-3.74312204214173</v>
       </c>
       <c r="G48">
-        <v>-4.334263376502811</v>
+        <v>-13.21462632668419</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.284126535193561</v>
       </c>
       <c r="E49">
-        <v>-23.75781224720673</v>
+        <v>-31.85385430591186</v>
       </c>
       <c r="F49">
-        <v>-3.956360125126074</v>
+        <v>-3.964423563794534</v>
       </c>
       <c r="G49">
-        <v>-4.305004775026732</v>
+        <v>-13.1016738234298</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.374666771241032</v>
       </c>
       <c r="E50">
-        <v>-23.67279467618673</v>
+        <v>-32.58871921821758</v>
       </c>
       <c r="F50">
-        <v>-3.608660658803175</v>
+        <v>-4.009938479951306</v>
       </c>
       <c r="G50">
-        <v>-5.322891590895366</v>
+        <v>-12.46515192204859</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.405540999149965</v>
       </c>
       <c r="E51">
-        <v>-23.44468185499835</v>
+        <v>-30.89407820354118</v>
       </c>
       <c r="F51">
-        <v>-3.505685724622428</v>
+        <v>-3.959354121159213</v>
       </c>
       <c r="G51">
-        <v>-5.312913606640002</v>
+        <v>-12.90689456608124</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>5.383574000484609</v>
       </c>
       <c r="E52">
-        <v>-23.73156521185827</v>
+        <v>-30.62631406394164</v>
       </c>
       <c r="F52">
-        <v>-3.860200669352422</v>
+        <v>-4.030766588298208</v>
       </c>
       <c r="G52">
-        <v>-5.524076753862415</v>
+        <v>-13.19768626515974</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>5.31713955618318</v>
       </c>
       <c r="E53">
-        <v>-22.40121728872892</v>
+        <v>-29.92258920314967</v>
       </c>
       <c r="F53">
-        <v>-4.108687294896702</v>
+        <v>-4.474042706617879</v>
       </c>
       <c r="G53">
-        <v>-5.149558047550205</v>
+        <v>-13.20772052868927</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>5.214659925951904</v>
       </c>
       <c r="E54">
-        <v>-22.3596413688645</v>
+        <v>-29.51883498909978</v>
       </c>
       <c r="F54">
-        <v>-3.577162331850999</v>
+        <v>-3.886007157244508</v>
       </c>
       <c r="G54">
-        <v>-5.806611952365975</v>
+        <v>-13.08253555966727</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>5.084572963052179</v>
       </c>
       <c r="E55">
-        <v>-22.70362878296115</v>
+        <v>-28.5160746114483</v>
       </c>
       <c r="F55">
-        <v>-3.504019665999386</v>
+        <v>-4.346495783306132</v>
       </c>
       <c r="G55">
-        <v>-5.027193663327663</v>
+        <v>-13.38223593679195</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>4.934398372318515</v>
       </c>
       <c r="E56">
-        <v>-20.23445115943484</v>
+        <v>-29.28087952965573</v>
       </c>
       <c r="F56">
-        <v>-3.699597844320665</v>
+        <v>-3.72524833718008</v>
       </c>
       <c r="G56">
-        <v>-5.844540872609405</v>
+        <v>-13.4382404356798</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>4.771876327465845</v>
       </c>
       <c r="E57">
-        <v>-20.90632273405686</v>
+        <v>-29.2864676665812</v>
       </c>
       <c r="F57">
-        <v>-3.498254184614229</v>
+        <v>-4.484625029544845</v>
       </c>
       <c r="G57">
-        <v>-5.383391810625547</v>
+        <v>-14.5736549287381</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>4.601256981418556</v>
       </c>
       <c r="E58">
-        <v>-19.26257271027866</v>
+        <v>-28.92530375057346</v>
       </c>
       <c r="F58">
-        <v>-3.629391369236277</v>
+        <v>-3.930333502111742</v>
       </c>
       <c r="G58">
-        <v>-6.451072541950357</v>
+        <v>-12.95831726994273</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>4.425159421645524</v>
       </c>
       <c r="E59">
-        <v>-19.80802740450256</v>
+        <v>-27.90162408724354</v>
       </c>
       <c r="F59">
-        <v>-3.915569403715058</v>
+        <v>-4.156024264709187</v>
       </c>
       <c r="G59">
-        <v>-6.696052911856426</v>
+        <v>-14.56107651096164</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>4.248593104709772</v>
       </c>
       <c r="E60">
-        <v>-19.44228520127306</v>
+        <v>-27.63990093197024</v>
       </c>
       <c r="F60">
-        <v>-3.785216153521153</v>
+        <v>-3.95025335511614</v>
       </c>
       <c r="G60">
-        <v>-6.312221640942245</v>
+        <v>-14.0040970872525</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>4.072426829054533</v>
       </c>
       <c r="E61">
-        <v>-18.97871437405586</v>
+        <v>-30.06688676316708</v>
       </c>
       <c r="F61">
-        <v>-3.753216583646741</v>
+        <v>-4.209636669211601</v>
       </c>
       <c r="G61">
-        <v>-6.231563509423443</v>
+        <v>-13.89346362114836</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>3.897103074154479</v>
       </c>
       <c r="E62">
-        <v>-19.62667560591738</v>
+        <v>-27.6366947723728</v>
       </c>
       <c r="F62">
-        <v>-3.658298753310793</v>
+        <v>-4.343090023734979</v>
       </c>
       <c r="G62">
-        <v>-7.139997068672692</v>
+        <v>-14.41103762130356</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>3.728488165544577</v>
       </c>
       <c r="E63">
-        <v>-18.88227146311451</v>
+        <v>-26.06178208198521</v>
       </c>
       <c r="F63">
-        <v>-4.15846792293671</v>
+        <v>-5.070364997193787</v>
       </c>
       <c r="G63">
-        <v>-6.301379604301133</v>
+        <v>-15.02605421886167</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>3.568837236265294</v>
       </c>
       <c r="E64">
-        <v>-18.58268573666307</v>
+        <v>-29.04510905892039</v>
       </c>
       <c r="F64">
-        <v>-4.386390127169009</v>
+        <v>-4.233150742791088</v>
       </c>
       <c r="G64">
-        <v>-6.310006885976473</v>
+        <v>-14.00466981163079</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>3.421069857850831</v>
       </c>
       <c r="E65">
-        <v>-18.47350875681214</v>
+        <v>-28.25031205736015</v>
       </c>
       <c r="F65">
-        <v>-4.118878442462555</v>
+        <v>-4.575391174823468</v>
       </c>
       <c r="G65">
-        <v>-6.435364003366516</v>
+        <v>-14.88934193027192</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>3.293419147848037</v>
       </c>
       <c r="E66">
-        <v>-18.39179244334373</v>
+        <v>-28.94867520492705</v>
       </c>
       <c r="F66">
-        <v>-3.670608899391504</v>
+        <v>-4.685925929191565</v>
       </c>
       <c r="G66">
-        <v>-7.259305819362486</v>
+        <v>-14.74121819120831</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>3.189212510940516</v>
       </c>
       <c r="E67">
-        <v>-18.40857949649017</v>
+        <v>-27.19025516232662</v>
       </c>
       <c r="F67">
-        <v>-4.108730054956419</v>
+        <v>-4.837771652363899</v>
       </c>
       <c r="G67">
-        <v>-7.125801449400297</v>
+        <v>-14.36795252638272</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>3.111870825658099</v>
       </c>
       <c r="E68">
-        <v>-18.95060160741625</v>
+        <v>-27.94517442177531</v>
       </c>
       <c r="F68">
-        <v>-4.060175215294961</v>
+        <v>-4.580011636831763</v>
       </c>
       <c r="G68">
-        <v>-6.808124809997373</v>
+        <v>-13.94376901589036</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>3.067558422383755</v>
       </c>
       <c r="E69">
-        <v>-18.07267540849721</v>
+        <v>-28.30970299397075</v>
       </c>
       <c r="F69">
-        <v>-4.041901624589663</v>
+        <v>-4.724394145877588</v>
       </c>
       <c r="G69">
-        <v>-7.160396650285681</v>
+        <v>-14.93122364188924</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>3.056873970949739</v>
       </c>
       <c r="E70">
-        <v>-19.46384526602358</v>
+        <v>-27.31525463036035</v>
       </c>
       <c r="F70">
-        <v>-4.317928104150477</v>
+        <v>-5.069442488498042</v>
       </c>
       <c r="G70">
-        <v>-6.467734517649509</v>
+        <v>-15.09523137845028</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>3.080511767843128</v>
       </c>
       <c r="E71">
-        <v>-18.42936519218537</v>
+        <v>-26.17376218724688</v>
       </c>
       <c r="F71">
-        <v>-4.041502530698972</v>
+        <v>-5.322080799099647</v>
       </c>
       <c r="G71">
-        <v>-6.601589805438861</v>
+        <v>-14.10514983456598</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>3.140579701028043</v>
       </c>
       <c r="E72">
-        <v>-19.26382709757879</v>
+        <v>-28.43648215228949</v>
       </c>
       <c r="F72">
-        <v>-4.38650098658309</v>
+        <v>-4.828085706985071</v>
       </c>
       <c r="G72">
-        <v>-7.670422606611339</v>
+        <v>-14.99343044784492</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>3.233735097240973</v>
       </c>
       <c r="E73">
-        <v>-18.93547650423062</v>
+        <v>-26.45864848706942</v>
       </c>
       <c r="F73">
-        <v>-4.013400461082457</v>
+        <v>-4.955737154887236</v>
       </c>
       <c r="G73">
-        <v>-6.917445644795186</v>
+        <v>-14.61202580681102</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>3.358031046363957</v>
       </c>
       <c r="E74">
-        <v>-18.2052736559158</v>
+        <v>-28.1571794609184</v>
       </c>
       <c r="F74">
-        <v>-4.450203973325726</v>
+        <v>-4.617867751181469</v>
       </c>
       <c r="G74">
-        <v>-7.715988955413867</v>
+        <v>-14.33516653863454</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>3.511548036520709</v>
       </c>
       <c r="E75">
-        <v>-18.26287131681936</v>
+        <v>-27.27522292013254</v>
       </c>
       <c r="F75">
-        <v>-4.633148929559545</v>
+        <v>-4.964565523512854</v>
       </c>
       <c r="G75">
-        <v>-6.874822370977069</v>
+        <v>-14.21672515087604</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>3.687247605761054</v>
       </c>
       <c r="E76">
-        <v>-20.21468889886537</v>
+        <v>-27.63992357434027</v>
       </c>
       <c r="F76">
-        <v>-4.566346630340393</v>
+        <v>-4.943350990922585</v>
       </c>
       <c r="G76">
-        <v>-6.232804964000669</v>
+        <v>-13.74739076504633</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>3.881219574199763</v>
       </c>
       <c r="E77">
-        <v>-19.50720993312103</v>
+        <v>-28.71304964535994</v>
       </c>
       <c r="F77">
-        <v>-4.83608025444621</v>
+        <v>-4.538875667531181</v>
       </c>
       <c r="G77">
-        <v>-6.191161611662177</v>
+        <v>-14.28487273080193</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>4.089781853811648</v>
       </c>
       <c r="E78">
-        <v>-20.17377866468007</v>
+        <v>-28.98279725657484</v>
       </c>
       <c r="F78">
-        <v>-4.375994681540065</v>
+        <v>-5.443703870434693</v>
       </c>
       <c r="G78">
-        <v>-5.487730274386756</v>
+        <v>-14.00742087497393</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>4.304735126103417</v>
       </c>
       <c r="E79">
-        <v>-20.39836380461647</v>
+        <v>-29.85556325936214</v>
       </c>
       <c r="F79">
-        <v>-4.638189073635431</v>
+        <v>-4.866245892870542</v>
       </c>
       <c r="G79">
-        <v>-7.379620975896219</v>
+        <v>-13.19407445997639</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>4.523228539916651</v>
       </c>
       <c r="E80">
-        <v>-20.53098922287911</v>
+        <v>-28.25375369760598</v>
       </c>
       <c r="F80">
-        <v>-4.651028969344856</v>
+        <v>-4.944724063951271</v>
       </c>
       <c r="G80">
-        <v>-5.739278766642738</v>
+        <v>-13.52247064583548</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>4.742714417965147</v>
       </c>
       <c r="E81">
-        <v>-20.83459623424937</v>
+        <v>-29.94980759617277</v>
       </c>
       <c r="F81">
-        <v>-4.843825368225666</v>
+        <v>-5.586571564772401</v>
       </c>
       <c r="G81">
-        <v>-5.549008472318666</v>
+        <v>-13.11445915030246</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>4.956467620533199</v>
       </c>
       <c r="E82">
-        <v>-23.08996195750352</v>
+        <v>-30.09961857329452</v>
       </c>
       <c r="F82">
-        <v>-4.978341389418304</v>
+        <v>-5.555195975028672</v>
       </c>
       <c r="G82">
-        <v>-6.059408520290262</v>
+        <v>-13.88178070594028</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>5.163082738694387</v>
       </c>
       <c r="E83">
-        <v>-22.06452071778462</v>
+        <v>-32.09972553792132</v>
       </c>
       <c r="F83">
-        <v>-4.928247187607039</v>
+        <v>-5.243637469549059</v>
       </c>
       <c r="G83">
-        <v>-5.370901122305876</v>
+        <v>-14.00979784667112</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>5.360837042244529</v>
       </c>
       <c r="E84">
-        <v>-24.69330893618528</v>
+        <v>-32.50699611203815</v>
       </c>
       <c r="F84">
-        <v>-5.167569698871628</v>
+        <v>-5.066747021029965</v>
       </c>
       <c r="G84">
-        <v>-5.862354918156223</v>
+        <v>-13.00741928138121</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>5.543074130805282</v>
       </c>
       <c r="E85">
-        <v>-24.14990111221285</v>
+        <v>-33.51083200226645</v>
       </c>
       <c r="F85">
-        <v>-4.649957592293061</v>
+        <v>-5.427914322457762</v>
       </c>
       <c r="G85">
-        <v>-5.855267040156644</v>
+        <v>-13.05644846081781</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>5.707251969513617</v>
       </c>
       <c r="E86">
-        <v>-24.91107872274014</v>
+        <v>-32.19145430742068</v>
       </c>
       <c r="F86">
-        <v>-5.250835412934731</v>
+        <v>-5.204327513168979</v>
       </c>
       <c r="G86">
-        <v>-6.035082631667698</v>
+        <v>-13.07685135297634</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.84981868224402</v>
       </c>
       <c r="E87">
-        <v>-26.15587471491658</v>
+        <v>-34.34500861379739</v>
       </c>
       <c r="F87">
-        <v>-5.200536913060374</v>
+        <v>-5.658741835191934</v>
       </c>
       <c r="G87">
-        <v>-6.236724649919166</v>
+        <v>-13.47200137908929</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.962432334012706</v>
       </c>
       <c r="E88">
-        <v>-26.67364684753159</v>
+        <v>-34.77079385389459</v>
       </c>
       <c r="F88">
-        <v>-4.737729741538547</v>
+        <v>-5.153667928345901</v>
       </c>
       <c r="G88">
-        <v>-5.490617070097001</v>
+        <v>-13.80583679126939</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>6.038740075715014</v>
       </c>
       <c r="E89">
-        <v>-28.35811690958675</v>
+        <v>-35.8164954863238</v>
       </c>
       <c r="F89">
-        <v>-4.817140715403469</v>
+        <v>-5.636333188341424</v>
       </c>
       <c r="G89">
-        <v>-4.967180093791755</v>
+        <v>-12.81939353693276</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>6.072104943788849</v>
       </c>
       <c r="E90">
-        <v>-29.78212726061675</v>
+        <v>-36.87548592572853</v>
       </c>
       <c r="F90">
-        <v>-5.296053384232358</v>
+        <v>-5.757287935780154</v>
       </c>
       <c r="G90">
-        <v>-5.069240902221947</v>
+        <v>-13.88443245291723</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>6.053500780812359</v>
       </c>
       <c r="E91">
-        <v>-31.12793765824529</v>
+        <v>-36.56877464542602</v>
       </c>
       <c r="F91">
-        <v>-5.629950853502203</v>
+        <v>-5.931648414099334</v>
       </c>
       <c r="G91">
-        <v>-5.922424766966299</v>
+        <v>-12.2623876288593</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.973919526497637</v>
       </c>
       <c r="E92">
-        <v>-31.77111682155471</v>
+        <v>-38.6412534174064</v>
       </c>
       <c r="F92">
-        <v>-5.10914599579811</v>
+        <v>-5.420638777482233</v>
       </c>
       <c r="G92">
-        <v>-5.071439104460023</v>
+        <v>-13.3542187898931</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.825643140512228</v>
       </c>
       <c r="E93">
-        <v>-34.77734202730968</v>
+        <v>-41.01710824858263</v>
       </c>
       <c r="F93">
-        <v>-5.303525308741401</v>
+        <v>-5.975277928363774</v>
       </c>
       <c r="G93">
-        <v>-6.335858936092642</v>
+        <v>-14.05055231753232</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>5.601792872823443</v>
       </c>
       <c r="E94">
-        <v>-35.66509275058836</v>
+        <v>-41.34177945679956</v>
       </c>
       <c r="F94">
-        <v>-5.536306322722268</v>
+        <v>-5.520209535797742</v>
       </c>
       <c r="G94">
-        <v>-6.252552368142422</v>
+        <v>-13.94432022172265</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>5.297222495584728</v>
       </c>
       <c r="E95">
-        <v>-37.94073698044885</v>
+        <v>-41.39733930439967</v>
       </c>
       <c r="F95">
-        <v>-5.59932356480352</v>
+        <v>-6.144514722120028</v>
       </c>
       <c r="G95">
-        <v>-6.984543781785135</v>
+        <v>-12.83604889154083</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.902192647875298</v>
       </c>
       <c r="E96">
-        <v>-39.65386096178756</v>
+        <v>-46.84311459248575</v>
       </c>
       <c r="F96">
-        <v>-5.671049605713772</v>
+        <v>-5.793986361105675</v>
       </c>
       <c r="G96">
-        <v>-7.506057331132064</v>
+        <v>-13.32458940731662</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.427338877558931</v>
       </c>
       <c r="E97">
-        <v>-41.46382862401729</v>
+        <v>-46.66386627007714</v>
       </c>
       <c r="F97">
-        <v>-5.481325596308915</v>
+        <v>-5.987353685969</v>
       </c>
       <c r="G97">
-        <v>-6.13881857614076</v>
+        <v>-13.34640921296596</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.85418121858778</v>
       </c>
       <c r="E98">
-        <v>-44.15627133730676</v>
+        <v>-48.78240867966355</v>
       </c>
       <c r="F98">
-        <v>-5.811533030795786</v>
+        <v>-5.760085552279778</v>
       </c>
       <c r="G98">
-        <v>-7.103018274999033</v>
+        <v>-14.56605888199824</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.216532240942375</v>
       </c>
       <c r="E99">
-        <v>-45.69747633141827</v>
+        <v>-49.43999744726538</v>
       </c>
       <c r="F99">
-        <v>-5.56299651851517</v>
+        <v>-5.487353181023077</v>
       </c>
       <c r="G99">
-        <v>-6.981590775164105</v>
+        <v>-14.32896092102118</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.480296759344714</v>
       </c>
       <c r="E100">
-        <v>-47.66007847431354</v>
+        <v>-50.97694341157266</v>
       </c>
       <c r="F100">
-        <v>-5.58369317927109</v>
+        <v>-5.917182052414751</v>
       </c>
       <c r="G100">
-        <v>-7.279523320970815</v>
+        <v>-14.21686088324315</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.727845317462604</v>
       </c>
       <c r="E101">
-        <v>-49.49385345652009</v>
+        <v>-52.78241203487578</v>
       </c>
       <c r="F101">
-        <v>-5.773899427127199</v>
+        <v>-5.974670577145203</v>
       </c>
       <c r="G101">
-        <v>-7.776806987515819</v>
+        <v>-14.97041719052867</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.8516960872098135</v>
       </c>
       <c r="E102">
-        <v>-51.92932678012581</v>
+        <v>-54.59830180898904</v>
       </c>
       <c r="F102">
-        <v>-6.012824428207013</v>
+        <v>-5.912469735463361</v>
       </c>
       <c r="G102">
-        <v>-9.352341957292527</v>
+        <v>-14.06706366340944</v>
       </c>
     </row>
   </sheetData>
